--- a/resources/templates/standard/L2300-01.xlsx
+++ b/resources/templates/standard/L2300-01.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>한도견본 관리대장</t>
   </si>
@@ -540,12 +543,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -580,21 +585,21 @@
       <c r="AJ1" s="2"/>
       <c r="AK1" s="2"/>
       <c r="AL1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM1" s="3"/>
       <c r="AN1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO1" s="4"/>
       <c r="AP1" s="4"/>
       <c r="AQ1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR1" s="4"/>
       <c r="AS1" s="4"/>
       <c r="AT1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU1" s="4"/>
       <c r="AV1" s="4"/>
@@ -701,30 +706,30 @@
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
       <c r="L4" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
       <c r="P4" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
@@ -734,13 +739,13 @@
       <c r="V4" s="4"/>
       <c r="W4" s="4"/>
       <c r="X4" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
       <c r="AA4" s="4"/>
       <c r="AB4" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AC4" s="4"/>
       <c r="AD4" s="4"/>
@@ -749,7 +754,7 @@
       <c r="AG4" s="4"/>
       <c r="AH4" s="4"/>
       <c r="AI4" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ4" s="4"/>
       <c r="AK4" s="4"/>
@@ -758,7 +763,7 @@
       <c r="AN4" s="4"/>
       <c r="AO4" s="4"/>
       <c r="AP4" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ4" s="4"/>
       <c r="AR4" s="4"/>
@@ -796,7 +801,7 @@
       <c r="Z5" s="5"/>
       <c r="AA5" s="5"/>
       <c r="AB5" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC5" s="8"/>
       <c r="AD5" s="8"/>
@@ -805,7 +810,7 @@
       <c r="AG5" s="5"/>
       <c r="AH5" s="5"/>
       <c r="AI5" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ5" s="8"/>
       <c r="AK5" s="8"/>
@@ -814,7 +819,7 @@
       <c r="AN5" s="5"/>
       <c r="AO5" s="5"/>
       <c r="AP5" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ5" s="8"/>
       <c r="AR5" s="8"/>
@@ -852,7 +857,7 @@
       <c r="Z6" s="5"/>
       <c r="AA6" s="5"/>
       <c r="AB6" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC6" s="8"/>
       <c r="AD6" s="8"/>
@@ -861,7 +866,7 @@
       <c r="AG6" s="5"/>
       <c r="AH6" s="5"/>
       <c r="AI6" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ6" s="8"/>
       <c r="AK6" s="8"/>
@@ -870,7 +875,7 @@
       <c r="AN6" s="5"/>
       <c r="AO6" s="5"/>
       <c r="AP6" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ6" s="8"/>
       <c r="AR6" s="8"/>
@@ -908,7 +913,7 @@
       <c r="Z7" s="5"/>
       <c r="AA7" s="5"/>
       <c r="AB7" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AC7" s="8"/>
       <c r="AD7" s="8"/>
@@ -917,7 +922,7 @@
       <c r="AG7" s="5"/>
       <c r="AH7" s="5"/>
       <c r="AI7" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ7" s="8"/>
       <c r="AK7" s="8"/>
